--- a/public/exports/29189595.xlsx
+++ b/public/exports/29189595.xlsx
@@ -59,7 +59,7 @@
       </c>
       <c r="J1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Areal (m²)</t>
+          <t xml:space="preserve">Opvarmet BBR-areal (m²)</t>
         </is>
       </c>
       <c r="K1" t="inlineStr">
@@ -6664,7 +6664,7 @@
       </c>
       <c r="K89" t="inlineStr">
         <is>
-          <t xml:space="preserve">311420439</t>
+          <t xml:space="preserve">311420440</t>
         </is>
       </c>
       <c r="L89" t="inlineStr">
@@ -6739,7 +6739,7 @@
       </c>
       <c r="K90" t="inlineStr">
         <is>
-          <t xml:space="preserve">311420439</t>
+          <t xml:space="preserve">311420440</t>
         </is>
       </c>
       <c r="L90" t="inlineStr">
@@ -6814,7 +6814,7 @@
       </c>
       <c r="K91" t="inlineStr">
         <is>
-          <t xml:space="preserve">311420439</t>
+          <t xml:space="preserve">311420440</t>
         </is>
       </c>
       <c r="L91" t="inlineStr">
@@ -6889,7 +6889,7 @@
       </c>
       <c r="K92" t="inlineStr">
         <is>
-          <t xml:space="preserve">311420439</t>
+          <t xml:space="preserve">311420440</t>
         </is>
       </c>
       <c r="L92" t="inlineStr">
@@ -6964,7 +6964,7 @@
       </c>
       <c r="K93" t="inlineStr">
         <is>
-          <t xml:space="preserve">311420439</t>
+          <t xml:space="preserve">311420440</t>
         </is>
       </c>
       <c r="L93" t="inlineStr">
@@ -7414,7 +7414,7 @@
       </c>
       <c r="K99" t="inlineStr">
         <is>
-          <t xml:space="preserve">311420439</t>
+          <t xml:space="preserve">311420440</t>
         </is>
       </c>
       <c r="L99" t="inlineStr">
@@ -7489,7 +7489,7 @@
       </c>
       <c r="K100" t="inlineStr">
         <is>
-          <t xml:space="preserve">311420439</t>
+          <t xml:space="preserve">311420440</t>
         </is>
       </c>
       <c r="L100" t="inlineStr">
@@ -7564,7 +7564,7 @@
       </c>
       <c r="K101" t="inlineStr">
         <is>
-          <t xml:space="preserve">311420439</t>
+          <t xml:space="preserve">311420440</t>
         </is>
       </c>
       <c r="L101" t="inlineStr">
@@ -7639,7 +7639,7 @@
       </c>
       <c r="K102" t="inlineStr">
         <is>
-          <t xml:space="preserve">311420439</t>
+          <t xml:space="preserve">311420440</t>
         </is>
       </c>
       <c r="L102" t="inlineStr">
@@ -7714,7 +7714,7 @@
       </c>
       <c r="K103" t="inlineStr">
         <is>
-          <t xml:space="preserve">311420439</t>
+          <t xml:space="preserve">311420440</t>
         </is>
       </c>
       <c r="L103" t="inlineStr">

--- a/public/exports/29189595.xlsx
+++ b/public/exports/29189595.xlsx
@@ -6664,7 +6664,7 @@
       </c>
       <c r="K89" t="inlineStr">
         <is>
-          <t xml:space="preserve">311420440</t>
+          <t xml:space="preserve">311420439</t>
         </is>
       </c>
       <c r="L89" t="inlineStr">
@@ -6739,7 +6739,7 @@
       </c>
       <c r="K90" t="inlineStr">
         <is>
-          <t xml:space="preserve">311420440</t>
+          <t xml:space="preserve">311420439</t>
         </is>
       </c>
       <c r="L90" t="inlineStr">
@@ -6814,7 +6814,7 @@
       </c>
       <c r="K91" t="inlineStr">
         <is>
-          <t xml:space="preserve">311420440</t>
+          <t xml:space="preserve">311420439</t>
         </is>
       </c>
       <c r="L91" t="inlineStr">
@@ -6889,7 +6889,7 @@
       </c>
       <c r="K92" t="inlineStr">
         <is>
-          <t xml:space="preserve">311420440</t>
+          <t xml:space="preserve">311420439</t>
         </is>
       </c>
       <c r="L92" t="inlineStr">
@@ -6964,7 +6964,7 @@
       </c>
       <c r="K93" t="inlineStr">
         <is>
-          <t xml:space="preserve">311420440</t>
+          <t xml:space="preserve">311420439</t>
         </is>
       </c>
       <c r="L93" t="inlineStr">
@@ -7414,7 +7414,7 @@
       </c>
       <c r="K99" t="inlineStr">
         <is>
-          <t xml:space="preserve">311420440</t>
+          <t xml:space="preserve">311420439</t>
         </is>
       </c>
       <c r="L99" t="inlineStr">
@@ -7489,7 +7489,7 @@
       </c>
       <c r="K100" t="inlineStr">
         <is>
-          <t xml:space="preserve">311420440</t>
+          <t xml:space="preserve">311420439</t>
         </is>
       </c>
       <c r="L100" t="inlineStr">
@@ -7564,7 +7564,7 @@
       </c>
       <c r="K101" t="inlineStr">
         <is>
-          <t xml:space="preserve">311420440</t>
+          <t xml:space="preserve">311420439</t>
         </is>
       </c>
       <c r="L101" t="inlineStr">
@@ -7639,7 +7639,7 @@
       </c>
       <c r="K102" t="inlineStr">
         <is>
-          <t xml:space="preserve">311420440</t>
+          <t xml:space="preserve">311420439</t>
         </is>
       </c>
       <c r="L102" t="inlineStr">
@@ -7714,7 +7714,7 @@
       </c>
       <c r="K103" t="inlineStr">
         <is>
-          <t xml:space="preserve">311420440</t>
+          <t xml:space="preserve">311420439</t>
         </is>
       </c>
       <c r="L103" t="inlineStr">
@@ -10316,30 +10316,30 @@
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rosenvænget 11</t>
+          <t xml:space="preserve">Biotekparken 1</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t xml:space="preserve">4270</t>
+          <t xml:space="preserve">4400</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t xml:space="preserve">8386414</t>
+          <t xml:space="preserve">100046682</t>
         </is>
       </c>
       <c r="I138" t="inlineStr">
         <is>
-          <t xml:space="preserve">8</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J138">
-        <v>5120</v>
+        <v>798</v>
       </c>
       <c r="K138" t="inlineStr">
         <is>
-          <t xml:space="preserve">311549608</t>
+          <t xml:space="preserve">311558253</t>
         </is>
       </c>
       <c r="L138" t="inlineStr">
@@ -10349,7 +10349,7 @@
       </c>
       <c r="M138" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-09-21</t>
+          <t xml:space="preserve">2031-10-28</t>
         </is>
       </c>
       <c r="N138" t="inlineStr">
@@ -10391,30 +10391,30 @@
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rosenvænget 13</t>
+          <t xml:space="preserve">Biotekparken 1</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t xml:space="preserve">4270</t>
+          <t xml:space="preserve">4400</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t xml:space="preserve">8386414</t>
+          <t xml:space="preserve">100046682</t>
         </is>
       </c>
       <c r="I139" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J139">
-        <v>682</v>
+        <v>683</v>
       </c>
       <c r="K139" t="inlineStr">
         <is>
-          <t xml:space="preserve">311549608</t>
+          <t xml:space="preserve">311558254</t>
         </is>
       </c>
       <c r="L139" t="inlineStr">
@@ -10424,7 +10424,7 @@
       </c>
       <c r="M139" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-09-21</t>
+          <t xml:space="preserve">2031-10-28</t>
         </is>
       </c>
       <c r="N139" t="inlineStr">
@@ -10466,30 +10466,30 @@
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rosenvænget 23</t>
+          <t xml:space="preserve">Elise Sørensens Vej 2</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t xml:space="preserve">4270</t>
+          <t xml:space="preserve">4400</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t xml:space="preserve">8386414</t>
+          <t xml:space="preserve">1352997</t>
         </is>
       </c>
       <c r="I140" t="inlineStr">
         <is>
-          <t xml:space="preserve">10</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J140">
-        <v>431</v>
+        <v>1771</v>
       </c>
       <c r="K140" t="inlineStr">
         <is>
-          <t xml:space="preserve">311549608</t>
+          <t xml:space="preserve">311558244</t>
         </is>
       </c>
       <c r="L140" t="inlineStr">
@@ -10499,7 +10499,7 @@
       </c>
       <c r="M140" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-09-21</t>
+          <t xml:space="preserve">2031-10-28</t>
         </is>
       </c>
       <c r="N140" t="inlineStr">
@@ -10541,30 +10541,30 @@
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rosenvænget 23</t>
+          <t xml:space="preserve">Elledevej 59</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t xml:space="preserve">4270</t>
+          <t xml:space="preserve">4400</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t xml:space="preserve">8386414</t>
+          <t xml:space="preserve">2459947</t>
         </is>
       </c>
       <c r="I141" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="J141">
-        <v>3294</v>
+        <v>2103</v>
       </c>
       <c r="K141" t="inlineStr">
         <is>
-          <t xml:space="preserve">311549608</t>
+          <t xml:space="preserve">311558263</t>
         </is>
       </c>
       <c r="L141" t="inlineStr">
@@ -10574,7 +10574,7 @@
       </c>
       <c r="M141" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-09-21</t>
+          <t xml:space="preserve">2031-10-28</t>
         </is>
       </c>
       <c r="N141" t="inlineStr">
@@ -10616,30 +10616,30 @@
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rosenvænget 25</t>
+          <t xml:space="preserve">Rynkevangen 14C</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t xml:space="preserve">4270</t>
+          <t xml:space="preserve">4400</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t xml:space="preserve">8386414</t>
+          <t xml:space="preserve">5342669</t>
         </is>
       </c>
       <c r="I142" t="inlineStr">
         <is>
-          <t xml:space="preserve">11</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J142">
-        <v>1326</v>
+        <v>980</v>
       </c>
       <c r="K142" t="inlineStr">
         <is>
-          <t xml:space="preserve">311549608</t>
+          <t xml:space="preserve">311558264</t>
         </is>
       </c>
       <c r="L142" t="inlineStr">
@@ -10649,7 +10649,7 @@
       </c>
       <c r="M142" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-09-21</t>
+          <t xml:space="preserve">2031-10-28</t>
         </is>
       </c>
       <c r="N142" t="inlineStr">
@@ -10691,30 +10691,30 @@
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rosenvænget 25</t>
+          <t xml:space="preserve">Torvet 3</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t xml:space="preserve">4270</t>
+          <t xml:space="preserve">4400</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t xml:space="preserve">8386414</t>
+          <t xml:space="preserve">5341684</t>
         </is>
       </c>
       <c r="I143" t="inlineStr">
         <is>
-          <t xml:space="preserve">12</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J143">
-        <v>408</v>
+        <v>1510</v>
       </c>
       <c r="K143" t="inlineStr">
         <is>
-          <t xml:space="preserve">311549608</t>
+          <t xml:space="preserve">311558248</t>
         </is>
       </c>
       <c r="L143" t="inlineStr">
@@ -10724,7 +10724,7 @@
       </c>
       <c r="M143" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-09-21</t>
+          <t xml:space="preserve">2031-10-28</t>
         </is>
       </c>
       <c r="N143" t="inlineStr">
@@ -10766,7 +10766,7 @@
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rosenvænget 25</t>
+          <t xml:space="preserve">Hyldens Kvarter 9</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
@@ -10776,30 +10776,30 @@
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t xml:space="preserve">8386414</t>
+          <t xml:space="preserve">100430394, 100562924</t>
         </is>
       </c>
       <c r="I144" t="inlineStr">
         <is>
-          <t xml:space="preserve">13</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="J144">
-        <v>754</v>
+        <v>593</v>
       </c>
       <c r="K144" t="inlineStr">
         <is>
-          <t xml:space="preserve">311549608</t>
+          <t xml:space="preserve">311562885</t>
         </is>
       </c>
       <c r="L144" t="inlineStr">
         <is>
-          <t xml:space="preserve">SEAS-NVE Strømmen A/S</t>
+          <t xml:space="preserve">Jysk Trykprøvning A/S</t>
         </is>
       </c>
       <c r="M144" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-09-21</t>
+          <t xml:space="preserve">2031-11-19</t>
         </is>
       </c>
       <c r="N144" t="inlineStr">
@@ -10841,40 +10841,40 @@
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rosenvænget 27</t>
+          <t xml:space="preserve">Klostermosen 2</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t xml:space="preserve">4270</t>
+          <t xml:space="preserve">4400</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t xml:space="preserve">8386414</t>
+          <t xml:space="preserve">275985</t>
         </is>
       </c>
       <c r="I145" t="inlineStr">
         <is>
-          <t xml:space="preserve">27</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="J145">
-        <v>341</v>
+        <v>414</v>
       </c>
       <c r="K145" t="inlineStr">
         <is>
-          <t xml:space="preserve">311549608</t>
+          <t xml:space="preserve">311586360</t>
         </is>
       </c>
       <c r="L145" t="inlineStr">
         <is>
-          <t xml:space="preserve">SEAS-NVE Strømmen A/S</t>
+          <t xml:space="preserve">Energi- og Bygningsrådgivning A/S</t>
         </is>
       </c>
       <c r="M145" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-09-21</t>
+          <t xml:space="preserve">2032-03-18</t>
         </is>
       </c>
       <c r="N145" t="inlineStr">
@@ -10916,17 +10916,17 @@
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t xml:space="preserve">Biotekparken 1</t>
+          <t xml:space="preserve">Centret 9</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t xml:space="preserve">4400</t>
+          <t xml:space="preserve">4470</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t xml:space="preserve">100046682</t>
+          <t xml:space="preserve">9921582</t>
         </is>
       </c>
       <c r="I146" t="inlineStr">
@@ -10935,21 +10935,21 @@
         </is>
       </c>
       <c r="J146">
-        <v>798</v>
+        <v>633</v>
       </c>
       <c r="K146" t="inlineStr">
         <is>
-          <t xml:space="preserve">311558253</t>
+          <t xml:space="preserve">311594043</t>
         </is>
       </c>
       <c r="L146" t="inlineStr">
         <is>
-          <t xml:space="preserve">SEAS-NVE Strømmen A/S</t>
+          <t xml:space="preserve">Rådgivende Ingeniør Ole Lentz ApS</t>
         </is>
       </c>
       <c r="M146" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-10-28</t>
+          <t xml:space="preserve">2032-04-21</t>
         </is>
       </c>
       <c r="N146" t="inlineStr">
@@ -10991,40 +10991,40 @@
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t xml:space="preserve">Biotekparken 1</t>
+          <t xml:space="preserve">Odinsvej 20</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t xml:space="preserve">4400</t>
+          <t xml:space="preserve">4270</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t xml:space="preserve">100046682</t>
+          <t xml:space="preserve">2472174</t>
         </is>
       </c>
       <c r="I147" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J147">
-        <v>683</v>
+        <v>2864</v>
       </c>
       <c r="K147" t="inlineStr">
         <is>
-          <t xml:space="preserve">311558254</t>
+          <t xml:space="preserve">311617056</t>
         </is>
       </c>
       <c r="L147" t="inlineStr">
         <is>
-          <t xml:space="preserve">SEAS-NVE Strømmen A/S</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="M147" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-10-28</t>
+          <t xml:space="preserve">2032-07-26</t>
         </is>
       </c>
       <c r="N147" t="inlineStr">
@@ -11066,7 +11066,7 @@
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t xml:space="preserve">Elise Sørensens Vej 2</t>
+          <t xml:space="preserve">Bredgade 26</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
@@ -11076,7 +11076,7 @@
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t xml:space="preserve">1352997</t>
+          <t xml:space="preserve">5341470</t>
         </is>
       </c>
       <c r="I148" t="inlineStr">
@@ -11085,21 +11085,21 @@
         </is>
       </c>
       <c r="J148">
-        <v>1771</v>
+        <v>1011</v>
       </c>
       <c r="K148" t="inlineStr">
         <is>
-          <t xml:space="preserve">311558244</t>
+          <t xml:space="preserve">311620368</t>
         </is>
       </c>
       <c r="L148" t="inlineStr">
         <is>
-          <t xml:space="preserve">SEAS-NVE Strømmen A/S</t>
+          <t xml:space="preserve">Andel Energi A/S</t>
         </is>
       </c>
       <c r="M148" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-10-28</t>
+          <t xml:space="preserve">2032-08-15</t>
         </is>
       </c>
       <c r="N148" t="inlineStr">
@@ -11141,7 +11141,7 @@
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t xml:space="preserve">Elledevej 59</t>
+          <t xml:space="preserve">Melbygade 2B</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
@@ -11151,30 +11151,30 @@
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t xml:space="preserve">2459947</t>
+          <t xml:space="preserve">2459072</t>
         </is>
       </c>
       <c r="I149" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J149">
-        <v>2103</v>
+        <v>308</v>
       </c>
       <c r="K149" t="inlineStr">
         <is>
-          <t xml:space="preserve">311558263</t>
+          <t xml:space="preserve">311620364</t>
         </is>
       </c>
       <c r="L149" t="inlineStr">
         <is>
-          <t xml:space="preserve">SEAS-NVE Strømmen A/S</t>
+          <t xml:space="preserve">Andel Energi A/S</t>
         </is>
       </c>
       <c r="M149" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-10-28</t>
+          <t xml:space="preserve">2032-08-15</t>
         </is>
       </c>
       <c r="N149" t="inlineStr">
@@ -11216,7 +11216,7 @@
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rynkevangen 14C</t>
+          <t xml:space="preserve">Radiovej 1</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
@@ -11226,30 +11226,30 @@
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t xml:space="preserve">5342669</t>
+          <t xml:space="preserve">9416235</t>
         </is>
       </c>
       <c r="I150" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="J150">
-        <v>980</v>
+        <v>252</v>
       </c>
       <c r="K150" t="inlineStr">
         <is>
-          <t xml:space="preserve">311558264</t>
+          <t xml:space="preserve">311620792</t>
         </is>
       </c>
       <c r="L150" t="inlineStr">
         <is>
-          <t xml:space="preserve">SEAS-NVE Strømmen A/S</t>
+          <t xml:space="preserve">Andel Energi A/S</t>
         </is>
       </c>
       <c r="M150" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-10-28</t>
+          <t xml:space="preserve">2032-08-16</t>
         </is>
       </c>
       <c r="N150" t="inlineStr">
@@ -11291,7 +11291,7 @@
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t xml:space="preserve">Torvet 3</t>
+          <t xml:space="preserve">Radiovej 5</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
@@ -11301,30 +11301,30 @@
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t xml:space="preserve">5341684</t>
+          <t xml:space="preserve">9416235</t>
         </is>
       </c>
       <c r="I151" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">19</t>
         </is>
       </c>
       <c r="J151">
-        <v>1510</v>
+        <v>486</v>
       </c>
       <c r="K151" t="inlineStr">
         <is>
-          <t xml:space="preserve">311558248</t>
+          <t xml:space="preserve">311620791</t>
         </is>
       </c>
       <c r="L151" t="inlineStr">
         <is>
-          <t xml:space="preserve">SEAS-NVE Strømmen A/S</t>
+          <t xml:space="preserve">Andel Energi A/S</t>
         </is>
       </c>
       <c r="M151" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-10-28</t>
+          <t xml:space="preserve">2032-08-16</t>
         </is>
       </c>
       <c r="N151" t="inlineStr">
@@ -11366,40 +11366,40 @@
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hyldens Kvarter 9</t>
+          <t xml:space="preserve">Algade 14</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t xml:space="preserve">4270</t>
+          <t xml:space="preserve">4281</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t xml:space="preserve">100430394, 100562924</t>
+          <t xml:space="preserve">2474884</t>
         </is>
       </c>
       <c r="I152" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J152">
-        <v>593</v>
+        <v>357</v>
       </c>
       <c r="K152" t="inlineStr">
         <is>
-          <t xml:space="preserve">311562885</t>
+          <t xml:space="preserve">311622694</t>
         </is>
       </c>
       <c r="L152" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jysk Trykprøvning A/S</t>
+          <t xml:space="preserve">Andel Energi A/S</t>
         </is>
       </c>
       <c r="M152" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-11-19</t>
+          <t xml:space="preserve">2032-08-24</t>
         </is>
       </c>
       <c r="N152" t="inlineStr">
@@ -11441,7 +11441,7 @@
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t xml:space="preserve">Klostermosen 2</t>
+          <t xml:space="preserve">Langagervej 15</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
@@ -11451,30 +11451,30 @@
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t xml:space="preserve">275985</t>
+          <t xml:space="preserve">5343581</t>
         </is>
       </c>
       <c r="I153" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J153">
-        <v>414</v>
+        <v>653</v>
       </c>
       <c r="K153" t="inlineStr">
         <is>
-          <t xml:space="preserve">311586360</t>
+          <t xml:space="preserve">311622692</t>
         </is>
       </c>
       <c r="L153" t="inlineStr">
         <is>
-          <t xml:space="preserve">Energi- og Bygningsrådgivning A/S</t>
+          <t xml:space="preserve">Andel Energi A/S</t>
         </is>
       </c>
       <c r="M153" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-03-18</t>
+          <t xml:space="preserve">2032-08-24</t>
         </is>
       </c>
       <c r="N153" t="inlineStr">
@@ -11516,40 +11516,40 @@
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t xml:space="preserve">Centret 9</t>
+          <t xml:space="preserve">Omfartsvejen 5</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t xml:space="preserve">4470</t>
+          <t xml:space="preserve">4281</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t xml:space="preserve">9921582</t>
+          <t xml:space="preserve">7544797</t>
         </is>
       </c>
       <c r="I154" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="J154">
-        <v>633</v>
+        <v>403</v>
       </c>
       <c r="K154" t="inlineStr">
         <is>
-          <t xml:space="preserve">311594043</t>
+          <t xml:space="preserve">311622697</t>
         </is>
       </c>
       <c r="L154" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rådgivende Ingeniør Ole Lentz ApS</t>
+          <t xml:space="preserve">Andel Energi A/S</t>
         </is>
       </c>
       <c r="M154" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-04-21</t>
+          <t xml:space="preserve">2032-08-24</t>
         </is>
       </c>
       <c r="N154" t="inlineStr">
@@ -11591,17 +11591,17 @@
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t xml:space="preserve">Odinsvej 20</t>
+          <t xml:space="preserve">Røsnæsvej 225</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t xml:space="preserve">4270</t>
+          <t xml:space="preserve">4400</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t xml:space="preserve">2472174</t>
+          <t xml:space="preserve">7761346</t>
         </is>
       </c>
       <c r="I155" t="inlineStr">
@@ -11610,21 +11610,21 @@
         </is>
       </c>
       <c r="J155">
-        <v>2864</v>
+        <v>350</v>
       </c>
       <c r="K155" t="inlineStr">
         <is>
-          <t xml:space="preserve">311617056</t>
+          <t xml:space="preserve">311622695</t>
         </is>
       </c>
       <c r="L155" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Andel Energi A/S</t>
         </is>
       </c>
       <c r="M155" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-07-26</t>
+          <t xml:space="preserve">2032-08-24</t>
         </is>
       </c>
       <c r="N155" t="inlineStr">
@@ -11666,7 +11666,7 @@
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bredgade 26</t>
+          <t xml:space="preserve">Græsmarken 19B</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
@@ -11676,7 +11676,7 @@
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t xml:space="preserve">5341470</t>
+          <t xml:space="preserve">8316898</t>
         </is>
       </c>
       <c r="I156" t="inlineStr">
@@ -11685,11 +11685,11 @@
         </is>
       </c>
       <c r="J156">
-        <v>1011</v>
+        <v>362</v>
       </c>
       <c r="K156" t="inlineStr">
         <is>
-          <t xml:space="preserve">311620368</t>
+          <t xml:space="preserve">311629060</t>
         </is>
       </c>
       <c r="L156" t="inlineStr">
@@ -11699,7 +11699,7 @@
       </c>
       <c r="M156" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-08-15</t>
+          <t xml:space="preserve">2032-09-19</t>
         </is>
       </c>
       <c r="N156" t="inlineStr">
@@ -11741,7 +11741,7 @@
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t xml:space="preserve">Melbygade 2B</t>
+          <t xml:space="preserve">Stadion Alle 13</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
@@ -11751,20 +11751,20 @@
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t xml:space="preserve">2459072</t>
+          <t xml:space="preserve">8116851</t>
         </is>
       </c>
       <c r="I157" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J157">
-        <v>308</v>
+        <v>709</v>
       </c>
       <c r="K157" t="inlineStr">
         <is>
-          <t xml:space="preserve">311620364</t>
+          <t xml:space="preserve">311629056</t>
         </is>
       </c>
       <c r="L157" t="inlineStr">
@@ -11774,7 +11774,7 @@
       </c>
       <c r="M157" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-08-15</t>
+          <t xml:space="preserve">2032-09-19</t>
         </is>
       </c>
       <c r="N157" t="inlineStr">
@@ -11816,7 +11816,7 @@
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t xml:space="preserve">Radiovej 1</t>
+          <t xml:space="preserve">Røsnæsvej 69B</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
@@ -11826,30 +11826,30 @@
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t xml:space="preserve">9416235</t>
+          <t xml:space="preserve">276423</t>
         </is>
       </c>
       <c r="I158" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J158">
-        <v>252</v>
+        <v>1452</v>
       </c>
       <c r="K158" t="inlineStr">
         <is>
-          <t xml:space="preserve">311620792</t>
+          <t xml:space="preserve">311677823</t>
         </is>
       </c>
       <c r="L158" t="inlineStr">
         <is>
-          <t xml:space="preserve">Andel Energi A/S</t>
+          <t xml:space="preserve">NRGi Rådgivning A/S</t>
         </is>
       </c>
       <c r="M158" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-08-16</t>
+          <t xml:space="preserve">2033-05-02</t>
         </is>
       </c>
       <c r="N158" t="inlineStr">
@@ -11891,7 +11891,7 @@
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t xml:space="preserve">Radiovej 5</t>
+          <t xml:space="preserve">Frederik Andersensvej 1</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
@@ -11901,30 +11901,30 @@
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t xml:space="preserve">9416235</t>
+          <t xml:space="preserve">5342092</t>
         </is>
       </c>
       <c r="I159" t="inlineStr">
         <is>
-          <t xml:space="preserve">19</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="J159">
-        <v>486</v>
+        <v>395</v>
       </c>
       <c r="K159" t="inlineStr">
         <is>
-          <t xml:space="preserve">311620791</t>
+          <t xml:space="preserve">311803915</t>
         </is>
       </c>
       <c r="L159" t="inlineStr">
         <is>
-          <t xml:space="preserve">Andel Energi A/S</t>
+          <t xml:space="preserve">Jysk Trykprøvning A/S</t>
         </is>
       </c>
       <c r="M159" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-08-16</t>
+          <t xml:space="preserve">2034-12-20</t>
         </is>
       </c>
       <c r="N159" t="inlineStr">
@@ -11966,40 +11966,40 @@
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t xml:space="preserve">Algade 14</t>
+          <t xml:space="preserve">Rosenvænget 11</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t xml:space="preserve">4281</t>
+          <t xml:space="preserve">4270</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t xml:space="preserve">2474884</t>
+          <t xml:space="preserve">8386414</t>
         </is>
       </c>
       <c r="I160" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">8</t>
         </is>
       </c>
       <c r="J160">
-        <v>357</v>
+        <v>5120</v>
       </c>
       <c r="K160" t="inlineStr">
         <is>
-          <t xml:space="preserve">311622694</t>
+          <t xml:space="preserve">311929839</t>
         </is>
       </c>
       <c r="L160" t="inlineStr">
         <is>
-          <t xml:space="preserve">Andel Energi A/S</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="M160" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-08-24</t>
+          <t xml:space="preserve">2036-10-05</t>
         </is>
       </c>
       <c r="N160" t="inlineStr">
@@ -12041,40 +12041,40 @@
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t xml:space="preserve">Langagervej 15</t>
+          <t xml:space="preserve">Rosenvænget 13</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t xml:space="preserve">4400</t>
+          <t xml:space="preserve">4270</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t xml:space="preserve">5343581</t>
+          <t xml:space="preserve">8386414</t>
         </is>
       </c>
       <c r="I161" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="J161">
-        <v>653</v>
+        <v>682</v>
       </c>
       <c r="K161" t="inlineStr">
         <is>
-          <t xml:space="preserve">311622692</t>
+          <t xml:space="preserve">311929839</t>
         </is>
       </c>
       <c r="L161" t="inlineStr">
         <is>
-          <t xml:space="preserve">Andel Energi A/S</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="M161" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-08-24</t>
+          <t xml:space="preserve">2036-10-05</t>
         </is>
       </c>
       <c r="N161" t="inlineStr">
@@ -12116,40 +12116,40 @@
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t xml:space="preserve">Omfartsvejen 5</t>
+          <t xml:space="preserve">Rosenvænget 23</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t xml:space="preserve">4281</t>
+          <t xml:space="preserve">4270</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t xml:space="preserve">7544797</t>
+          <t xml:space="preserve">8386414</t>
         </is>
       </c>
       <c r="I162" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">10</t>
         </is>
       </c>
       <c r="J162">
-        <v>403</v>
+        <v>431</v>
       </c>
       <c r="K162" t="inlineStr">
         <is>
-          <t xml:space="preserve">311622697</t>
+          <t xml:space="preserve">311929839</t>
         </is>
       </c>
       <c r="L162" t="inlineStr">
         <is>
-          <t xml:space="preserve">Andel Energi A/S</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="M162" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-08-24</t>
+          <t xml:space="preserve">2036-10-05</t>
         </is>
       </c>
       <c r="N162" t="inlineStr">
@@ -12191,40 +12191,40 @@
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t xml:space="preserve">Røsnæsvej 225</t>
+          <t xml:space="preserve">Rosenvænget 23</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t xml:space="preserve">4400</t>
+          <t xml:space="preserve">4270</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t xml:space="preserve">7761346</t>
+          <t xml:space="preserve">8386414</t>
         </is>
       </c>
       <c r="I163" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J163">
-        <v>350</v>
+        <v>3294</v>
       </c>
       <c r="K163" t="inlineStr">
         <is>
-          <t xml:space="preserve">311622695</t>
+          <t xml:space="preserve">311929839</t>
         </is>
       </c>
       <c r="L163" t="inlineStr">
         <is>
-          <t xml:space="preserve">Andel Energi A/S</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="M163" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-08-24</t>
+          <t xml:space="preserve">2036-10-05</t>
         </is>
       </c>
       <c r="N163" t="inlineStr">
@@ -12266,40 +12266,40 @@
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t xml:space="preserve">Græsmarken 19B</t>
+          <t xml:space="preserve">Rosenvænget 25</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t xml:space="preserve">4400</t>
+          <t xml:space="preserve">4270</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t xml:space="preserve">8316898</t>
+          <t xml:space="preserve">8386414</t>
         </is>
       </c>
       <c r="I164" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">11</t>
         </is>
       </c>
       <c r="J164">
-        <v>362</v>
+        <v>1326</v>
       </c>
       <c r="K164" t="inlineStr">
         <is>
-          <t xml:space="preserve">311629060</t>
+          <t xml:space="preserve">311929839</t>
         </is>
       </c>
       <c r="L164" t="inlineStr">
         <is>
-          <t xml:space="preserve">Andel Energi A/S</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="M164" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-09-19</t>
+          <t xml:space="preserve">2036-10-05</t>
         </is>
       </c>
       <c r="N164" t="inlineStr">
@@ -12341,40 +12341,40 @@
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t xml:space="preserve">Stadion Alle 13</t>
+          <t xml:space="preserve">Rosenvænget 25</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t xml:space="preserve">4400</t>
+          <t xml:space="preserve">4270</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t xml:space="preserve">8116851</t>
+          <t xml:space="preserve">8386414</t>
         </is>
       </c>
       <c r="I165" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">12</t>
         </is>
       </c>
       <c r="J165">
-        <v>709</v>
+        <v>408</v>
       </c>
       <c r="K165" t="inlineStr">
         <is>
-          <t xml:space="preserve">311629056</t>
+          <t xml:space="preserve">311929839</t>
         </is>
       </c>
       <c r="L165" t="inlineStr">
         <is>
-          <t xml:space="preserve">Andel Energi A/S</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="M165" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-09-19</t>
+          <t xml:space="preserve">2036-10-05</t>
         </is>
       </c>
       <c r="N165" t="inlineStr">
@@ -12416,40 +12416,40 @@
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t xml:space="preserve">Røsnæsvej 69B</t>
+          <t xml:space="preserve">Rosenvænget 25</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t xml:space="preserve">4400</t>
+          <t xml:space="preserve">4270</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t xml:space="preserve">276423</t>
+          <t xml:space="preserve">8386414</t>
         </is>
       </c>
       <c r="I166" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">13</t>
         </is>
       </c>
       <c r="J166">
-        <v>1452</v>
+        <v>754</v>
       </c>
       <c r="K166" t="inlineStr">
         <is>
-          <t xml:space="preserve">311677823</t>
+          <t xml:space="preserve">311929839</t>
         </is>
       </c>
       <c r="L166" t="inlineStr">
         <is>
-          <t xml:space="preserve">NRGi Rådgivning A/S</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="M166" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-05-02</t>
+          <t xml:space="preserve">2036-10-05</t>
         </is>
       </c>
       <c r="N166" t="inlineStr">
@@ -12491,40 +12491,40 @@
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t xml:space="preserve">Frederik Andersensvej 1</t>
+          <t xml:space="preserve">Rosenvænget 27</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t xml:space="preserve">4400</t>
+          <t xml:space="preserve">4270</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t xml:space="preserve">5342092</t>
+          <t xml:space="preserve">8386414</t>
         </is>
       </c>
       <c r="I167" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">27</t>
         </is>
       </c>
       <c r="J167">
-        <v>395</v>
+        <v>341</v>
       </c>
       <c r="K167" t="inlineStr">
         <is>
-          <t xml:space="preserve">311803915</t>
+          <t xml:space="preserve">311929839</t>
         </is>
       </c>
       <c r="L167" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jysk Trykprøvning A/S</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="M167" t="inlineStr">
         <is>
-          <t xml:space="preserve">2034-12-20</t>
+          <t xml:space="preserve">2036-10-05</t>
         </is>
       </c>
       <c r="N167" t="inlineStr">
